--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ7"/>
+  <dimension ref="A1:AZ8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -786,48 +786,52 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125987256</v>
+        <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>93197</v>
+        <v>96569</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>2813</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Skogshakmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Rhytidiadelphus subpinnatus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Lindb.) T.J.Kop.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Basmyran, Mpd</t>
+          <t>Basmyran, Basmyran, Mpd</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529588</v>
+        <v>529606</v>
       </c>
       <c r="R3" t="n">
-        <v>6917303</v>
+        <v>6917253</v>
       </c>
       <c r="S3" t="n">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -851,22 +855,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2026-09-02</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>12:49</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,49 +885,49 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Lizette Karström</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Lizette Karström</t>
+          <t>Marie Israelsson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125987256</t>
+          <t>https://artportalen.se/Sighting/136648564</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>126553335</v>
+        <v>125987256</v>
       </c>
       <c r="B4" t="n">
-        <v>91872</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -933,13 +937,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>529389</v>
+        <v>529588</v>
       </c>
       <c r="R4" t="n">
-        <v>6917323</v>
+        <v>6917303</v>
       </c>
       <c r="S4" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -963,12 +967,22 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -994,38 +1008,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126553335</t>
+          <t>https://artportalen.se/Sighting/125987256</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125986872</v>
+        <v>126553335</v>
       </c>
       <c r="B5" t="n">
-        <v>79327</v>
+        <v>91872</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1035,13 +1049,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529588</v>
+        <v>529389</v>
       </c>
       <c r="R5" t="n">
-        <v>6917303</v>
+        <v>6917323</v>
       </c>
       <c r="S5" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1065,22 +1079,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2025-07-10</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1106,38 +1110,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125986872</t>
+          <t>https://artportalen.se/Sighting/126553335</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125988191</v>
+        <v>125986872</v>
       </c>
       <c r="B6" t="n">
-        <v>79946</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1147,10 +1151,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>529488</v>
+        <v>529588</v>
       </c>
       <c r="R6" t="n">
-        <v>6917221</v>
+        <v>6917303</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1182,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1192,7 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:16</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,38 +1222,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125988191</t>
+          <t>https://artportalen.se/Sighting/125986872</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126553641</v>
+        <v>125988191</v>
       </c>
       <c r="B7" t="n">
-        <v>57141</v>
+        <v>79946</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100138</v>
+        <v>6453</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1259,13 +1263,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>529389</v>
+        <v>529488</v>
       </c>
       <c r="R7" t="n">
-        <v>6917323</v>
+        <v>6917221</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1289,12 +1293,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2025-07-10</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>11:16</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1319,6 +1333,108 @@
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125988191</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126553641</v>
+      </c>
+      <c r="B8" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Basmyran, Mpd</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>529389</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6917323</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Haverö</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Lizette Karström</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Lizette Karström</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126553641</t>
         </is>
@@ -1332,6 +1448,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96569</v>
+        <v>96572</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96572</v>
+        <v>96573</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96573</v>
+        <v>96578</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96578</v>
+        <v>96580</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96580</v>
+        <v>96586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96586</v>
+        <v>96588</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96588</v>
+        <v>96589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96589</v>
+        <v>96595</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96595</v>
+        <v>96599</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96599</v>
+        <v>96601</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96601</v>
+        <v>96603</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96603</v>
+        <v>96616</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 20580-2026 artfynd.xlsx
+++ b/artfynd/A 20580-2026 artfynd.xlsx
@@ -789,7 +789,7 @@
         <v>136648564</v>
       </c>
       <c r="B3" t="n">
-        <v>96616</v>
+        <v>96618</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
